--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261028.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261028.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -711,7 +711,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17916,7 +17916,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18184,7 +18184,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19591,7 +19591,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19859,7 +19859,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20864,7 +20864,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21936,7 +21936,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22070,7 +22070,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22338,7 +22338,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22807,7 +22807,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23075,7 +23075,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23142,7 +23142,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23343,7 +23343,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23477,7 +23477,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S342" s="1" t="n">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S343" s="1" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S344" s="1" t="n">
@@ -23678,7 +23678,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S345" s="1" t="n">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S346" s="1" t="n">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S347" s="1" t="n">
@@ -23879,7 +23879,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S348" s="1" t="n">
@@ -23946,7 +23946,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S349" s="1" t="n">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S350" s="1" t="n">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S351" s="1" t="n">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S352" s="1" t="n">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S353" s="1" t="n">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S354" s="1" t="n">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S355" s="1" t="n">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S356" s="1" t="n">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S357" t="inlineStr"/>
@@ -24515,7 +24515,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S358" t="inlineStr"/>
@@ -24564,7 +24564,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S359" t="inlineStr"/>
@@ -24613,7 +24613,7 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="S360" t="inlineStr"/>
